--- a/CHOR_MATTATHIAS.xlsx
+++ b/CHOR_MATTATHIAS.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcus.silva05\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcus.silva05\Desktop\git_projetos\PYTHON_TESTE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C4C2FE-0AA7-4A16-8F74-34B4970E2044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEB0A58-3A96-4FF9-BB63-C6C17A0B2C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E61240CA-E029-443C-9C69-E83755505E61}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="2" r:id="rId1"/>
+    <sheet name="CHOR_2026" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'2026'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">CHOR_2026!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
